--- a/outputs/41601.xlsx
+++ b/outputs/41601.xlsx
@@ -183,12 +183,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -274,17 +278,17 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable13" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
-  <location ref="B3:C3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable15" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
+  <location ref="A3:B3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="1">
     <pivotField axis="axisPage" showAll="0">
       <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
         <item x="4"/>
-        <item x="5"/>
+        <item h="1" x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -390,6 +394,64 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable14" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
+  <location ref="A3:B3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisPage" showAll="0">
+      <items count="7">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="0" hier="-1"/>
+  </pageFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable13" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
+  <location ref="B3:C3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisPage" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="0" hier="-1"/>
+  </pageFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable16" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
   <location ref="A3:B3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="1">
@@ -401,64 +463,6 @@
         <item x="3"/>
         <item h="1" x="4"/>
         <item h="1" x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="0" hier="-1"/>
-  </pageFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable15" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
-  <location ref="A3:B3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="1">
-    <pivotField axis="axisPage" showAll="0">
-      <items count="7">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item x="4"/>
-        <item h="1" x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="0" hier="-1"/>
-  </pageFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable14" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
-  <location ref="A3:B3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="1">
-    <pivotField axis="axisPage" showAll="0">
-      <items count="7">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -656,82 +660,82 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="E2" s="0" t="n">
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="E2" s="1" t="n">
         <f aca="true">INDIRECT(A2&amp;"!C2")</f>
         <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="E3" s="0" t="n">
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="E3" s="1" t="n">
         <f aca="true">INDIRECT(A3&amp;"!C2")</f>
         <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <f aca="true">INDIRECT(A4&amp;"!C2")</f>
         <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <f aca="true">INDIRECT(A5&amp;"!C2")</f>
         <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <f aca="true">INDIRECT(A6&amp;"!C2")</f>
         <v>27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <f aca="true">INDIRECT(A7&amp;"!C2")</f>
         <v>17</v>
       </c>
@@ -755,35 +759,35 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="0" t="n">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="1" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7"/>
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -804,35 +808,35 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="0" t="n">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="1" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7"/>
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -853,35 +857,35 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="0" t="n">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="1" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7"/>
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -902,35 +906,35 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="0" t="n">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="1" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7"/>
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -951,35 +955,35 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="0" t="n">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="1" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7"/>
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1000,35 +1004,35 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="0" t="n">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="1" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7"/>
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/41601.xlsx
+++ b/outputs/41601.xlsx
@@ -278,17 +278,17 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable15" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
-  <location ref="A3:B3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable13" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
+  <location ref="B3:C3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="1">
     <pivotField axis="axisPage" showAll="0">
       <items count="7">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
         <item x="4"/>
-        <item h="1" x="5"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -394,6 +394,35 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable16" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
+  <location ref="A3:B3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisPage" showAll="0">
+      <items count="7">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="0" hier="-1"/>
+  </pageFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable14" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
   <location ref="A3:B3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="1">
@@ -422,37 +451,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable13" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
-  <location ref="B3:C3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="1">
-    <pivotField axis="axisPage" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="0" hier="-1"/>
-  </pageFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable16" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable15" cacheId="1" dataOnRows="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="1" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="1" compactData="1">
   <location ref="A3:B3" firstHeaderRow="0" firstDataRow="0" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="1">
     <pivotField axis="axisPage" showAll="0">
@@ -460,8 +460,8 @@
         <item h="1" x="0"/>
         <item h="1" x="1"/>
         <item h="1" x="2"/>
-        <item x="3"/>
-        <item h="1" x="4"/>
+        <item h="1" x="3"/>
+        <item x="4"/>
         <item h="1" x="5"/>
         <item t="default"/>
       </items>
@@ -687,7 +687,7 @@
       </c>
       <c r="C2" s="6"/>
       <c r="E2" s="1" t="n">
-        <f aca="true">INDIRECT(A2&amp;"!C2")</f>
+        <f aca="true">INDIRECT(""&amp;A2&amp;"!C2")</f>
         <v>33</v>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C3" s="8"/>
       <c r="E3" s="1" t="n">
-        <f aca="true">INDIRECT(A3&amp;"!C2")</f>
+        <f aca="true">INDIRECT(""&amp;A3&amp;"!C2")</f>
         <v>26</v>
       </c>
     </row>
@@ -709,7 +709,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="1" t="n">
-        <f aca="true">INDIRECT(A4&amp;"!C2")</f>
+        <f aca="true">INDIRECT(""&amp;A4&amp;"!C2")</f>
         <v>31</v>
       </c>
     </row>
@@ -718,7 +718,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="1" t="n">
-        <f aca="true">INDIRECT(A5&amp;"!C2")</f>
+        <f aca="true">INDIRECT(""&amp;A5&amp;"!C2")</f>
         <v>41</v>
       </c>
     </row>
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="n">
-        <f aca="true">INDIRECT(A6&amp;"!C2")</f>
+        <f aca="true">INDIRECT(""&amp;A6&amp;"!C2")</f>
         <v>27</v>
       </c>
     </row>
@@ -736,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="E7" s="1" t="n">
-        <f aca="true">INDIRECT(A7&amp;"!C2")</f>
+        <f aca="true">INDIRECT(""&amp;A7&amp;"!C2")</f>
         <v>17</v>
       </c>
     </row>
